--- a/data/trans_orig/P32-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2007</t>
+          <t>Población según si han pensado que deberían beber menos en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23742</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31167</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256971</t>
+          <t>257464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272555</t>
+          <t>272347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173836</t>
+          <t>172587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183594</t>
+          <t>183591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>435024</t>
+          <t>436720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>453847</t>
+          <t>454248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25314</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27566</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476567</t>
+          <t>477033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492714</t>
+          <t>492717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208381</t>
+          <t>207157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692591</t>
+          <t>692950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709711</t>
+          <t>709461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390859</t>
+          <t>390336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399938</t>
+          <t>399949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217563</t>
+          <t>216781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611077</t>
+          <t>612587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623127</t>
+          <t>622993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302071</t>
+          <t>302989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312422</t>
+          <t>312427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137702</t>
+          <t>138076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>444677</t>
+          <t>445392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456550</t>
+          <t>456532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162809</t>
+          <t>161988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175422</t>
+          <t>174704</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70090</t>
+          <t>68399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236823</t>
+          <t>236334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249934</t>
+          <t>249989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8880</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>8158</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119682</t>
+          <t>120969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151033</t>
+          <t>150311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,62 +2826,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2083</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4996</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68027</t>
+          <t>68073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84664</t>
+          <t>83990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69535</t>
+          <t>66093</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50238</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>83364</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1811369</t>
+          <t>1814811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1841713</t>
+          <t>1841980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>871892</t>
+          <t>871725</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>887622</t>
+          <t>887473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2693384</t>
+          <t>2692122</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2725248</t>
+          <t>2724698</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2012</t>
+          <t>Población según si han pensado que deberían beber menos en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40697</t>
+          <t>41540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47718</t>
+          <t>47564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241163</t>
+          <t>240320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262023</t>
+          <t>261416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172617</t>
+          <t>173664</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182645</t>
+          <t>182557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>418659</t>
+          <t>418813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441546</t>
+          <t>441597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33257</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60540</t>
+          <t>61149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415831</t>
+          <t>415714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439962</t>
+          <t>440710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195720</t>
+          <t>196328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209763</t>
+          <t>209712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619830</t>
+          <t>619221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>647113</t>
+          <t>646206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31477</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>395582</t>
+          <t>396286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414114</t>
+          <t>414435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228718</t>
+          <t>227706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241278</t>
+          <t>241215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631444</t>
+          <t>629086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652221</t>
+          <t>651338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42198</t>
+          <t>42871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43098</t>
+          <t>43435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351910</t>
+          <t>351237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>374496</t>
+          <t>374661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213312</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215488</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566498</t>
+          <t>566161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214761</t>
+          <t>214657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228608</t>
+          <t>228002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106964</t>
+          <t>104563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325318</t>
+          <t>324978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338874</t>
+          <t>339088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134176</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148406</t>
+          <t>148430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57482</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>190966</t>
+          <t>191425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206753</t>
+          <t>206772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,62 +5805,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>12142</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>12360</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>75816</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>97758</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114844</t>
+          <t>115514</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161660</t>
+          <t>162242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>34593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136494</t>
+          <t>133873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189385</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1878959</t>
+          <t>1878377</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1925775</t>
+          <t>1925105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1015720</t>
+          <t>1016215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1036542</t>
+          <t>1036945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2902042</t>
+          <t>2903987</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2954933</t>
+          <t>2957554</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2016</t>
+          <t>Población según si han pensado que deberían beber menos en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29257</t>
+          <t>30470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>45181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225915</t>
+          <t>224702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244079</t>
+          <t>244182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151615</t>
+          <t>151175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>164264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>382357</t>
+          <t>381587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405067</t>
+          <t>405164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23472</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46569</t>
+          <t>47478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329506</t>
+          <t>328613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349914</t>
+          <t>350100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210509</t>
+          <t>209947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221764</t>
+          <t>221130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545612</t>
+          <t>544703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568709</t>
+          <t>568370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>24746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407849</t>
+          <t>407406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423578</t>
+          <t>423384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241693</t>
+          <t>241653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248282</t>
+          <t>248279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653946</t>
+          <t>655708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670442</t>
+          <t>671008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37786</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>48822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>352876</t>
+          <t>353352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373649</t>
+          <t>373821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247841</t>
+          <t>248465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>260869</t>
+          <t>260914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>607985</t>
+          <t>607050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632792</t>
+          <t>631443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32415</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258347</t>
+          <t>259134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276026</t>
+          <t>276687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119191</t>
+          <t>119699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129514</t>
+          <t>129524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383762</t>
+          <t>384071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404045</t>
+          <t>404185</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168425</t>
+          <t>168957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62221</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234804</t>
+          <t>234571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>242135</t>
+          <t>242140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,62 +8784,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2426</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>9318</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2426</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87083</t>
+          <t>86834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>122874</t>
+          <t>122683</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>85564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129082</t>
+          <t>128607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27059</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51661</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118964</t>
+          <t>117227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>169567</t>
+          <t>165883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1871154</t>
+          <t>1871629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1914045</t>
+          <t>1914672</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1094646</t>
+          <t>1094789</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1119248</t>
+          <t>1119761</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2976976</t>
+          <t>2980660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3027579</t>
+          <t>3029316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2023</t>
+          <t>Población según si han pensado que deberían beber menos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37466</t>
+          <t>35929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140786</t>
+          <t>138953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166388</t>
+          <t>166138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85476</t>
+          <t>86122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99181</t>
+          <t>99142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>233287</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263073</t>
+          <t>263646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28725</t>
+          <t>29036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>34441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201410</t>
+          <t>201099</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222036</t>
+          <t>221614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130474</t>
+          <t>129435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140771</t>
+          <t>140991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337927</t>
+          <t>337947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360483</t>
+          <t>360150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>253406</t>
+          <t>254267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271667</t>
+          <t>271549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143412</t>
+          <t>143025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149520</t>
+          <t>149636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>401314</t>
+          <t>400802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>419138</t>
+          <t>419794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>320192</t>
+          <t>318567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335192</t>
+          <t>334959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183625</t>
+          <t>184281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190292</t>
+          <t>190237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>508558</t>
+          <t>507857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>524382</t>
+          <t>523986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34203</t>
+          <t>34226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>39719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>228811</t>
+          <t>228788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246188</t>
+          <t>246856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126020</t>
+          <t>125923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132539</t>
+          <t>132440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355751</t>
+          <t>358052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376249</t>
+          <t>375992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26387</t>
+          <t>25876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171859</t>
+          <t>172112</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183108</t>
+          <t>182867</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272767</t>
+          <t>272963</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>443008</t>
+          <t>443519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466168</t>
+          <t>466092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95138</t>
+          <t>95629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>122065</t>
+          <t>121623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126248</t>
+          <t>126240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76577</t>
+          <t>77979</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120635</t>
+          <t>121734</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93260</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150209</t>
+          <t>150627</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1458736</t>
+          <t>1457637</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1502794</t>
+          <t>1501392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>988971</t>
+          <t>989191</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1014440</t>
+          <t>1014166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2455820</t>
+          <t>2455402</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2512769</t>
+          <t>2512832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P32-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23249</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257464</t>
+          <t>255936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272347</t>
+          <t>272364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172587</t>
+          <t>172674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183591</t>
+          <t>183608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>436720</t>
+          <t>437057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>454248</t>
+          <t>454549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477033</t>
+          <t>478402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492717</t>
+          <t>493245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207157</t>
+          <t>207839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692950</t>
+          <t>691069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709461</t>
+          <t>709807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,77 +1434,77 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2160</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6860</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>13468</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2160</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7490</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>7014</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3068</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>13474</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390336</t>
+          <t>391077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399949</t>
+          <t>400018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>222111</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>217411</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>224271</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>619047</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>612593</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>623174</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>222111</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>216781</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>224271</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>619047</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>612587</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>622993</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302989</t>
+          <t>302947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312427</t>
+          <t>312431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138076</t>
+          <t>138072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>445392</t>
+          <t>444095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456532</t>
+          <t>456460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161988</t>
+          <t>161255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174704</t>
+          <t>174771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68399</t>
+          <t>71230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236334</t>
+          <t>237402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249989</t>
+          <t>250057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120969</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150311</t>
+          <t>150119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68073</t>
+          <t>68064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66093</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50788</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1814811</t>
+          <t>1812984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1841980</t>
+          <t>1841871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>871725</t>
+          <t>872331</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>887473</t>
+          <t>887415</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2692122</t>
+          <t>2693910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2724698</t>
+          <t>2725490</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47564</t>
+          <t>47178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240320</t>
+          <t>239473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>261416</t>
+          <t>260986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173664</t>
+          <t>173768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182557</t>
+          <t>182542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>418813</t>
+          <t>419199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441597</t>
+          <t>442094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51222</t>
+          <t>50378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34164</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61149</t>
+          <t>62260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415714</t>
+          <t>416558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440710</t>
+          <t>441034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196328</t>
+          <t>197155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209712</t>
+          <t>209549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619221</t>
+          <t>618110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>646206</t>
+          <t>646722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30773</t>
+          <t>30535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>40533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>396286</t>
+          <t>396524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414435</t>
+          <t>414514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227706</t>
+          <t>227506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241215</t>
+          <t>240482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629086</t>
+          <t>630889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651338</t>
+          <t>652128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42871</t>
+          <t>42624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351237</t>
+          <t>351484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>374661</t>
+          <t>374231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566161</t>
+          <t>566483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>590157</t>
+          <t>590827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214657</t>
+          <t>213558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228002</t>
+          <t>227941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104563</t>
+          <t>105634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324978</t>
+          <t>324954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339088</t>
+          <t>338941</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134168</t>
+          <t>133685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148430</t>
+          <t>149175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>191425</t>
+          <t>191623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206772</t>
+          <t>206783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>74115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97758</t>
+          <t>98801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>115514</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162242</t>
+          <t>163599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133873</t>
+          <t>135889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>187440</t>
+          <t>185844</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1878377</t>
+          <t>1877020</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1925105</t>
+          <t>1926156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1016215</t>
+          <t>1014989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1036945</t>
+          <t>1037069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2903987</t>
+          <t>2905583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2957554</t>
+          <t>2955538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>44030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224702</t>
+          <t>225910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244182</t>
+          <t>243780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151175</t>
+          <t>150933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164264</t>
+          <t>165036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>381587</t>
+          <t>382738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405164</t>
+          <t>404797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>36789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47478</t>
+          <t>45525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328613</t>
+          <t>329798</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350100</t>
+          <t>349644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209947</t>
+          <t>209772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221130</t>
+          <t>221529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>544703</t>
+          <t>546656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568370</t>
+          <t>568636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>21591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407406</t>
+          <t>409763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423384</t>
+          <t>423572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241653</t>
+          <t>241413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248279</t>
+          <t>248274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655708</t>
+          <t>653620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>671008</t>
+          <t>670975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>37681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48822</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353352</t>
+          <t>352981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373821</t>
+          <t>374070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>248465</t>
+          <t>249129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>260914</t>
+          <t>261881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>607050</t>
+          <t>608558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>631443</t>
+          <t>632683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>32733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>259134</t>
+          <t>259681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276687</t>
+          <t>276684</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119699</t>
+          <t>119489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129524</t>
+          <t>129518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384071</t>
+          <t>383444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404185</t>
+          <t>403438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168957</t>
+          <t>168580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62304</t>
+          <t>61966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234571</t>
+          <t>234167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>242140</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86834</t>
+          <t>87672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>122683</t>
+          <t>123915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85564</t>
+          <t>86421</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128607</t>
+          <t>127534</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117227</t>
+          <t>120909</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165883</t>
+          <t>168154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1871629</t>
+          <t>1872702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1914672</t>
+          <t>1913815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1094789</t>
+          <t>1094384</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1119761</t>
+          <t>1118886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2980660</t>
+          <t>2978389</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3029316</t>
+          <t>3025634</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>22896</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>158541</t>
+          <t>152895</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138953</t>
+          <t>136489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166138</t>
+          <t>161338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94953</t>
+          <t>103292</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86122</t>
+          <t>92765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99142</t>
+          <t>109380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>253493</t>
+          <t>256188</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234824</t>
+          <t>237427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263646</t>
+          <t>266869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29036</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34441</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>214256</t>
+          <t>231208</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201099</t>
+          <t>218724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221614</t>
+          <t>239564</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>137130</t>
+          <t>147624</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129435</t>
+          <t>140347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140991</t>
+          <t>151590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>351387</t>
+          <t>378832</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337947</t>
+          <t>365818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360150</t>
+          <t>388153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27916</t>
+          <t>33930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>25609</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>264544</t>
+          <t>290779</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>254267</t>
+          <t>278854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271549</t>
+          <t>298591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>147454</t>
+          <t>166332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143025</t>
+          <t>162158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149636</t>
+          <t>168976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>411998</t>
+          <t>457111</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>400802</t>
+          <t>446257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>419794</t>
+          <t>466577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>20935</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>328885</t>
+          <t>337663</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318567</t>
+          <t>328594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334959</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>188185</t>
+          <t>207157</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184281</t>
+          <t>202447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190237</t>
+          <t>209960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>517070</t>
+          <t>544819</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>507857</t>
+          <t>534317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>523986</t>
+          <t>552364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191830</t>
+          <t>212000</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191830</t>
+          <t>212000</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191830</t>
+          <t>212000</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>535934</t>
+          <t>565754</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>535934</t>
+          <t>565754</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>535934</t>
+          <t>565754</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>34861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>29420</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39719</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>238317</t>
+          <t>255781</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>228788</t>
+          <t>245786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246856</t>
+          <t>263176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>130033</t>
+          <t>142876</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125923</t>
+          <t>138050</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132440</t>
+          <t>145508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>368351</t>
+          <t>398657</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>358052</t>
+          <t>387032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375992</t>
+          <t>406893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25876</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>178308</t>
+          <t>194611</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172112</t>
+          <t>187868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182867</t>
+          <t>199920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>278226</t>
+          <t>77811</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272963</t>
+          <t>74114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>456534</t>
+          <t>272423</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>443519</t>
+          <t>265360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466092</t>
+          <t>278200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>469395</t>
+          <t>287382</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>469395</t>
+          <t>287382</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>469395</t>
+          <t>287382</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -11836,27 +11836,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>98783</t>
+          <t>108387</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95629</t>
+          <t>105123</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>26812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>124975</t>
+          <t>138076</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121623</t>
+          <t>134201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>139868</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77979</t>
+          <t>87427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121734</t>
+          <t>134739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93197</t>
+          <t>118684</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150627</t>
+          <t>169199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1481636</t>
+          <t>1571323</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1457637</t>
+          <t>1545770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1501392</t>
+          <t>1593082</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1002172</t>
+          <t>874782</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>989191</t>
+          <t>860505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1014166</t>
+          <t>884285</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2483807</t>
+          <t>2446105</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2455402</t>
+          <t>2417339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2512832</t>
+          <t>2467854</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
